--- a/artfynd/A 31358-2025 artfynd.xlsx
+++ b/artfynd/A 31358-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>97909332</v>
+        <v>104154059</v>
       </c>
       <c r="B2" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,38 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1204</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Pålkem, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>795304.5250519207</v>
+        <v>795303</v>
       </c>
       <c r="R2" t="n">
-        <v>7372701.505142531</v>
+        <v>7372701</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -752,24 +743,14 @@
           <t>2021-09-29</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-09-29</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering.</t>
+          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,15 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104154059</v>
+        <v>120288178</v>
       </c>
       <c r="B3" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -829,20 +805,24 @@
           <t>(Brot.) Murrill</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Pålkem, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>795302.5222187649</v>
+        <v>795304</v>
       </c>
       <c r="R3" t="n">
-        <v>7372701.292812819</v>
+        <v>7372701</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -869,24 +849,14 @@
           <t>2021-09-29</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-09-29</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
+          <t>Påträffad under Sveaskogs naturvärdesinventering.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -910,117 +880,6 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>120288178</v>
-      </c>
-      <c r="B4" t="n">
-        <v>90652</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>5442</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Tallticka</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Porodaedalea pini</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Pålkem, Nb</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>795304</v>
-      </c>
-      <c r="R4" t="n">
-        <v>7372701</v>
-      </c>
-      <c r="S4" t="n">
-        <v>5</v>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Boden</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Råneå</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2021-09-29</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>2021-09-29</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering.</t>
-        </is>
-      </c>
-      <c r="AD4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
